--- a/sheets/국악이꽃피는나무/검수/누나의 얼굴.xlsx
+++ b/sheets/국악이꽃피는나무/검수/누나의 얼굴.xlsx
@@ -2419,13 +2419,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
